--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5603.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5603.xlsx
@@ -1204,6 +1204,9 @@
       <c r="C12" t="n">
         <v>1.23</v>
       </c>
+      <c r="G12" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>5603-08-08-08-FG</t>
@@ -1216,12 +1219,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N1@DRIVE, N1_2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5603-08-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N1_2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5603-08-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5603-08-08-08 dims are NOT assumed; confirm before modelling | Brennan CAD record 5603-08-08-08-FG (PARTcommunity / CADENAS, N1@DRIVE=N1, N1_2@DRIVE=N; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5603-08-08-08 dims are NOT assumed; confirm before modelling | Brennan CAD record 5603-08-08-08-FG (PARTcommunity / CADENAS, N1@DRIVE=N1, N1_2@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1483,6 +1486,9 @@
       <c r="C16" t="n">
         <v>2.08</v>
       </c>
+      <c r="G16" t="n">
+        <v>1.72</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>5603-24-24-24-FG</t>
@@ -1495,12 +1501,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: N1@DRIVE, N1_2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N1_2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5603-24-24-24-FG (PARTcommunity / CADENAS, N1@DRIVE=N1, N1_2@DRIVE=N; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5603-24-24-24-FG (PARTcommunity / CADENAS, N1@DRIVE=N1, N1_2@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5603.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5603.xlsx
@@ -1204,9 +1204,21 @@
       <c r="C12" t="n">
         <v>1.23</v>
       </c>
+      <c r="D12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.531</v>
+      </c>
       <c r="G12" t="n">
         <v>0.7</v>
       </c>
+      <c r="H12" t="n">
+        <v>0.531</v>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>5603-08-08-08-FG</t>
@@ -1219,12 +1231,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N1_2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5603-08-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N1_2@DRIVE, N3@DRIVE, W@REF, D1_1@BORE, D1_3@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5603-08-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5603-08-08-08 dims are NOT assumed; confirm before modelling | Brennan CAD record 5603-08-08-08-FG (PARTcommunity / CADENAS, N1@DRIVE=N1, N1_2@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5603-08-08-08 dims are NOT assumed; confirm before modelling | Brennan CAD record 5603-08-08-08-FG (PARTcommunity / CADENAS, N1@DRIVE=N1, N1_2@DRIVE=N, N3@DRIVE=N2, W@REF=Y, D1_1@BORE=A1D, D1_3@BORE=A3D; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1486,9 +1498,21 @@
       <c r="C16" t="n">
         <v>2.08</v>
       </c>
+      <c r="D16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G16" t="n">
         <v>1.72</v>
       </c>
+      <c r="H16" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>5603-24-24-24-FG</t>
@@ -1501,12 +1525,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N1_2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: N1@DRIVE, N1_2@DRIVE, N3@DRIVE, W@REF, D1_1@BORE, D1_3@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5603-24-24-24-FG (PARTcommunity / CADENAS, N1@DRIVE=N1, N1_2@DRIVE=N; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5603-24-24-24-FG (PARTcommunity / CADENAS, N1@DRIVE=N1, N1_2@DRIVE=N, N3@DRIVE=N2, W@REF=Y, D1_1@BORE=A1D, D1_3@BORE=A3D; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
